--- a/testLeague.xlsx
+++ b/testLeague.xlsx
@@ -10,13 +10,14 @@
     <sheet name="Matching" sheetId="2" r:id="rId1"/>
     <sheet name="Team" sheetId="3" r:id="rId2"/>
     <sheet name="FirebaseRealtimeDatabase" sheetId="4" r:id="rId3"/>
+    <sheet name="DetailMatch" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
   <si>
     <t>พวกพี่เสือเก่า</t>
   </si>
@@ -154,13 +155,31 @@
   </si>
   <si>
     <t>G-SC448ZV16Y</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>Color_1</t>
+  </si>
+  <si>
+    <t>Color_2</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>League Name</t>
+  </si>
+  <si>
+    <t>CREATOR LEAGUE SS3 SSSSSSSSS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -183,13 +202,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -201,8 +213,23 @@
       <color rgb="FF146C2E"/>
       <name val="Google Sans Code"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,6 +239,96 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -269,15 +386,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -288,9 +405,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -299,13 +413,44 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0066FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -551,12 +696,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -570,9 +717,11 @@
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -586,9 +735,11 @@
         <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -604,7 +755,9 @@
       <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -614,13 +767,9 @@
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -1174,9 +1323,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Team!$A:$A</xm:f>
+            <xm:f>Team!$A$2:$A$50</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:C51</xm:sqref>
+          <xm:sqref>B2:C5 B7:C51</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1186,95 +1335,136 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="46.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="8" max="8" width="46.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="18">
+      <c r="A1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18.75" thickBot="1">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="18.75" thickBot="1">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="20"/>
+      <c r="H2" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="18">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="24"/>
+      <c r="C3" s="20"/>
+    </row>
+    <row r="4" spans="1:8" ht="18">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="18">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="30"/>
+    </row>
+    <row r="5" spans="1:8" ht="18">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="18">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="26"/>
+    </row>
+    <row r="6" spans="1:8" ht="18">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="18">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="20"/>
+    </row>
+    <row r="7" spans="1:8" ht="18">
+      <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="18">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="31"/>
+    </row>
+    <row r="8" spans="1:8" ht="18">
+      <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="18">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="22"/>
+      <c r="C8" s="26"/>
+    </row>
+    <row r="9" spans="1:8" ht="18">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="18">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="28"/>
+      <c r="C9" s="19"/>
+    </row>
+    <row r="10" spans="1:8" ht="18">
+      <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="18">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="29"/>
+      <c r="C10" s="26"/>
+    </row>
+    <row r="11" spans="1:8" ht="18">
+      <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="18">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" ht="18">
+      <c r="B11" s="27"/>
+      <c r="C11" s="21"/>
+    </row>
+    <row r="12" spans="1:8" ht="18">
       <c r="A12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" ht="18">
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:8" ht="18">
       <c r="A13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" ht="18">
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+    </row>
+    <row r="14" spans="1:8" ht="18">
       <c r="A14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" ht="18">
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+    </row>
+    <row r="15" spans="1:8" ht="18">
       <c r="A15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" ht="18">
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+    </row>
+    <row r="16" spans="1:8" ht="18">
       <c r="A16" s="2"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="150" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -1282,145 +1472,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="10" customFormat="1" ht="14.25">
-      <c r="A2" s="10" t="s">
+    <row r="3" spans="1:2" s="9" customFormat="1" ht="14.25">
+      <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="10" customFormat="1" ht="14.25">
-      <c r="A3" s="10" t="s">
+    <row r="4" spans="1:2" s="9" customFormat="1" ht="14.25">
+      <c r="A4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="10" customFormat="1" ht="14.25">
-      <c r="A4" s="10" t="s">
+    <row r="5" spans="1:2" s="9" customFormat="1" ht="14.25">
+      <c r="A5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="10" customFormat="1" ht="14.25">
-      <c r="A5" s="10" t="s">
+    <row r="6" spans="1:2" s="9" customFormat="1" ht="14.25">
+      <c r="A6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="10" customFormat="1" ht="14.25">
-      <c r="A6" s="10" t="s">
+    <row r="7" spans="1:2" s="9" customFormat="1" ht="14.25">
+      <c r="A7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="10" customFormat="1" ht="14.25">
-      <c r="A7" s="10" t="s">
+    <row r="8" spans="1:2" s="9" customFormat="1" ht="14.25">
+      <c r="A8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="10" customFormat="1">
-      <c r="A8" s="10" t="s">
+    <row r="9" spans="1:2" s="9" customFormat="1">
+      <c r="A9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="10" customFormat="1">
-      <c r="A9" s="10" t="s">
+    <row r="10" spans="1:2" s="9" customFormat="1">
+      <c r="A10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:2" s="10" customFormat="1">
-      <c r="A18" s="12" t="s">
+    <row r="19" spans="1:2" s="9" customFormat="1">
+      <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="11"/>
-    </row>
-    <row r="19" spans="1:2" s="10" customFormat="1">
-      <c r="A19" s="11" t="s">
+      <c r="B19" s="10"/>
+    </row>
+    <row r="20" spans="1:2" s="9" customFormat="1">
+      <c r="A20" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="10" customFormat="1">
-      <c r="A20" s="11" t="s">
+    <row r="21" spans="1:2" s="9" customFormat="1">
+      <c r="A21" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="10" customFormat="1">
-      <c r="A21" s="11" t="s">
+    <row r="22" spans="1:2" s="9" customFormat="1">
+      <c r="A22" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="10" customFormat="1">
-      <c r="A22" s="11" t="s">
+    <row r="23" spans="1:2" s="9" customFormat="1">
+      <c r="A23" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="10" customFormat="1">
-      <c r="A23" s="11" t="s">
+    <row r="24" spans="1:2" s="9" customFormat="1">
+      <c r="A24" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="10" customFormat="1">
-      <c r="A24" s="11" t="s">
+    <row r="25" spans="1:2" s="9" customFormat="1">
+      <c r="A25" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B25" s="11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="10" customFormat="1">
-      <c r="A25" s="11" t="s">
+    <row r="26" spans="1:2" s="9" customFormat="1">
+      <c r="A26" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="10" customFormat="1">
-      <c r="A26" s="11" t="s">
+    <row r="27" spans="1:2" s="9" customFormat="1">
+      <c r="A27" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>